--- a/reports and protocols/Touchpoints.xlsx
+++ b/reports and protocols/Touchpoints.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fd7d235552eefb0e/Documents/Schooljaar 25-26/Sem 2/PGO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fd7d235552eefb0e/Documents/Schooljaar 25-26/Sem 1/Project gebruiksgericht ontwerpen/TasteMate/reports and protocols/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="8_{96ABC54A-9408-4EF1-A94A-15C8853AE394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E481E0B7-5979-442F-9179-79E524415F26}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="8_{96ABC54A-9408-4EF1-A94A-15C8853AE394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB86C103-6C55-45D7-872A-91C581C3DBDD}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{2FF89E0D-8096-4289-AD0C-F6D10395187D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{2FF89E0D-8096-4289-AD0C-F6D10395187D}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -155,13 +155,13 @@
     <t>Cumulatief trauma</t>
   </si>
   <si>
-    <t>slecht kijkhoek</t>
-  </si>
-  <si>
     <t>Productoptismalisatie</t>
   </si>
   <si>
     <t>Hoek van scherm t.o.v. koelkast aanpasbaar maken</t>
+  </si>
+  <si>
+    <t>slechte kijkhoek</t>
   </si>
 </sst>
 </file>
@@ -269,15 +269,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -286,6 +277,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -432,8 +432,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="618740" y="1096865"/>
-          <a:ext cx="1820069" cy="2396092"/>
+          <a:off x="615565" y="1119090"/>
+          <a:ext cx="1823244" cy="2434192"/>
           <a:chOff x="621122" y="1645346"/>
           <a:chExt cx="1828006" cy="2413555"/>
         </a:xfrm>
@@ -1596,61 +1596,61 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
@@ -1777,11 +1777,11 @@
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
       <c r="E21" s="5"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1792,40 +1792,40 @@
       <c r="L21" s="1"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
       <c r="E23" s="5"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="3"/>
@@ -1833,11 +1833,11 @@
       <c r="D24" s="3"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
       <c r="E25" s="6"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -1852,32 +1852,32 @@
       <c r="D26" s="3"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="F27" s="11" t="s">
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="F27" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="J27" s="12" t="s">
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="J27" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B29" s="3"/>
@@ -1885,23 +1885,23 @@
       <c r="D29" s="3"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8" t="s">
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B32" s="2"/>
@@ -1909,11 +1909,11 @@
       <c r="D32" s="2"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3"/>
@@ -1921,47 +1921,47 @@
       <c r="D34" s="3"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8" t="s">
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8" t="s">
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="3"/>
@@ -1969,31 +1969,36 @@
       <c r="D39" s="3"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B41" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B41" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B27:D28"/>
-    <mergeCell ref="F27:H28"/>
-    <mergeCell ref="J27:L28"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
@@ -2003,21 +2008,16 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B27:D28"/>
+    <mergeCell ref="F27:H28"/>
+    <mergeCell ref="J27:L28"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="J22:L22"/>
     <mergeCell ref="J23:L23"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E37:G37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
